--- a/tests/ALiS_IndividualProfile_Baseline/baselines/Modify/NVRCP/Mammo.xlsx
+++ b/tests/ALiS_IndividualProfile_Baseline/baselines/Modify/NVRCP/Mammo.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="10668" windowHeight="9000" firstSheet="3" activeTab="3"/>
+    <workbookView windowWidth="22188" windowHeight="8400" firstSheet="3" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="TC01_Tabs" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="92">
   <si>
     <t>Tab Name</t>
   </si>
@@ -67,6 +67,9 @@
   </si>
   <si>
     <t>Home Address</t>
+  </si>
+  <si>
+    <t>Employment Details</t>
   </si>
   <si>
     <t>Violations</t>
@@ -1644,7 +1647,9 @@
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -1654,7 +1659,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
@@ -1665,7 +1670,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -1676,7 +1681,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -1687,7 +1692,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -1698,7 +1703,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -1798,10 +1803,10 @@
         <v>8</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
@@ -1818,10 +1823,10 @@
         <v>9</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
@@ -1838,10 +1843,10 @@
         <v>9</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
@@ -1858,10 +1863,10 @@
         <v>9</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>23</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>22</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
@@ -1878,10 +1883,10 @@
         <v>9</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
@@ -1898,10 +1903,10 @@
         <v>9</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -1918,10 +1923,10 @@
         <v>9</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -1938,10 +1943,10 @@
         <v>9</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
@@ -1958,10 +1963,10 @@
         <v>9</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
@@ -1978,10 +1983,10 @@
         <v>9</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
@@ -1998,10 +2003,10 @@
         <v>9</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
@@ -2018,10 +2023,10 @@
         <v>9</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
@@ -2038,10 +2043,10 @@
         <v>9</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
@@ -2058,10 +2063,10 @@
         <v>9</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
@@ -2078,10 +2083,10 @@
         <v>10</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
@@ -2098,10 +2103,10 @@
         <v>10</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
@@ -2118,10 +2123,10 @@
         <v>10</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
@@ -2138,10 +2143,10 @@
         <v>10</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
@@ -2158,10 +2163,10 @@
         <v>10</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
@@ -2178,10 +2183,10 @@
         <v>10</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
@@ -2198,10 +2203,10 @@
         <v>10</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
@@ -2218,10 +2223,10 @@
         <v>10</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
@@ -2238,10 +2243,10 @@
         <v>10</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
@@ -2258,10 +2263,10 @@
         <v>10</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -2278,10 +2283,10 @@
         <v>10</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
@@ -2298,10 +2303,10 @@
         <v>10</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -2315,13 +2320,13 @@
         <v>1</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -2335,13 +2340,13 @@
         <v>1</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
@@ -2355,13 +2360,13 @@
         <v>1</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
@@ -2375,13 +2380,13 @@
         <v>1</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
@@ -2395,13 +2400,13 @@
         <v>1</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
@@ -2415,13 +2420,13 @@
         <v>1</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
@@ -2435,13 +2440,13 @@
         <v>1</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
@@ -2455,13 +2460,13 @@
         <v>1</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
@@ -2475,13 +2480,13 @@
         <v>1</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
@@ -2495,13 +2500,13 @@
         <v>1</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
@@ -2515,13 +2520,13 @@
         <v>1</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -2529,13 +2534,13 @@
         <v>1</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -2562,10 +2567,10 @@
         <v>8</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
@@ -2587,9 +2592,11 @@
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4"/>
+      <c r="B2" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="C2" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -2614,9 +2621,11 @@
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4"/>
+      <c r="B3" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="C3" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D3" s="2">
         <v>2</v>
@@ -2641,9 +2650,11 @@
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4"/>
+      <c r="B4" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="C4" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
@@ -2669,10 +2680,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -2698,10 +2709,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D6" s="2">
         <v>2</v>
@@ -2727,10 +2738,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
@@ -2756,10 +2767,10 @@
         <v>2</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D8" s="2">
         <v>4</v>
@@ -2785,10 +2796,10 @@
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D9" s="2">
         <v>5</v>
@@ -2814,10 +2825,10 @@
         <v>2</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D10" s="2">
         <v>6</v>
@@ -2843,10 +2854,10 @@
         <v>3</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
@@ -2872,13 +2883,13 @@
         <v>3</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -2901,13 +2912,13 @@
         <v>3</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -2930,13 +2941,13 @@
         <v>3</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -2959,10 +2970,10 @@
         <v>3</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" s="2">
         <v>5</v>
@@ -2988,10 +2999,10 @@
         <v>3</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D16" s="2">
         <v>6</v>
@@ -3017,10 +3028,10 @@
         <v>3</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D17" s="2">
         <v>7</v>
@@ -3046,10 +3057,10 @@
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D18" s="2">
         <v>8</v>
@@ -3075,13 +3086,13 @@
         <v>4</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -3104,13 +3115,13 @@
         <v>4</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -3133,13 +3144,13 @@
         <v>4</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
@@ -3162,13 +3173,13 @@
         <v>4</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
@@ -3191,13 +3202,13 @@
         <v>4</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
@@ -3220,13 +3231,13 @@
         <v>4</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
@@ -3249,13 +3260,13 @@
         <v>4</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
@@ -3278,10 +3289,10 @@
         <v>5</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D26" s="2">
         <v>1</v>
@@ -3307,10 +3318,10 @@
         <v>5</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D27" s="2">
         <v>2</v>
@@ -3336,10 +3347,10 @@
         <v>5</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D28" s="2">
         <v>3</v>
@@ -3365,10 +3376,10 @@
         <v>5</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D29" s="2">
         <v>4</v>
@@ -3394,10 +3405,10 @@
         <v>5</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D30" s="2">
         <v>5</v>
@@ -3423,10 +3434,10 @@
         <v>5</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D31" s="2">
         <v>6</v>
@@ -3452,10 +3463,10 @@
         <v>5</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D32" s="2">
         <v>7</v>
@@ -3481,10 +3492,10 @@
         <v>5</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D33" s="2">
         <v>8</v>
@@ -3510,10 +3521,10 @@
         <v>5</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D34" s="2">
         <v>9</v>
@@ -3539,13 +3550,13 @@
         <v>6</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
@@ -3568,13 +3579,13 @@
         <v>6</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -3597,13 +3608,13 @@
         <v>6</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
@@ -3626,13 +3637,13 @@
         <v>6</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -3655,13 +3666,13 @@
         <v>6</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
@@ -3684,13 +3695,13 @@
         <v>6</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
@@ -3713,10 +3724,10 @@
         <v>6</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D41" s="2">
         <v>7</v>
@@ -3742,10 +3753,10 @@
         <v>6</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D42" s="2">
         <v>8</v>
@@ -3813,7 +3824,7 @@
         <v>8</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" ht="69" spans="1:3">
@@ -3824,7 +3835,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3832,19 +3843,21 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="C4" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3852,10 +3865,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3863,10 +3876,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3874,10 +3887,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
